--- a/files/九龙-九龙站-天玺.xlsx
+++ b/files/九龙-九龙站-天玺.xlsx
@@ -216,61 +216,61 @@
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -659,7 +659,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-九龙站-天玺.xlsx
+++ b/files/九龙-九龙站-天玺.xlsx
@@ -216,61 +216,61 @@
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -659,7 +659,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
